--- a/VerveStacks_ETH_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_ETH_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ETH_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F563630-768A-41C5-A698-95A94D209A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAE84632-5043-470D-8FB9-4AC94C5D3886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -756,10 +756,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>FaP,SaP,RaP,WaP,SaD,WaD,RaD,FaD</t>
+    <t>FaD,WaP,SaD,FaP,SaP,RaD,RaP,WaD</t>
   </si>
   <si>
-    <t>SaN,WaN,FaN,RaN,WaP,FaP,SaP,RaP</t>
+    <t>RaP,RaN,FaP,SaP,SaN,WaN,FaN,WaP</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>SaN,WaN,FaN,RaN,WaP,FaP,SaP,RaP</v>
+        <v>RaP,RaN,FaP,SaP,SaN,WaN,FaN,WaP</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>FaP,SaP,RaP,WaP,SaD,WaD,RaD,FaD</v>
+        <v>FaD,WaP,SaD,FaP,SaP,RaD,RaP,WaD</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1482,7 +1482,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DB7FD13-AA39-4F9D-996D-FDA7FB062B5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A6339DD-1445-425B-A12B-624665D905F3}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1566,7 +1566,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30191B66-47B7-44C1-87CC-74539603DBD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E60FA678-B2F1-4011-894F-15339028102B}">
   <dimension ref="B9:O514"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16172,7 +16172,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1618C7E-A050-48DC-BBD4-A0BDD77F7511}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B37295C1-4FA9-47C6-B840-C044753228A2}">
   <dimension ref="B9:BL78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23011,7 +23011,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43C06B17-0129-483D-9029-EFB9DD16CDB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{117FBA9D-82C7-4498-A7F3-5CCF1B147AAB}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23209,7 +23209,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8014892F-9E35-4D79-91E5-BCAD46343EB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A459569-2483-4303-91E2-74A476C1B315}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23500,7 +23500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{230F3B7A-F00C-41F0-A72F-215A42401BB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6C00C5E-0165-4AB3-98C1-AEA19C0B4467}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23659,7 +23659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97503400-DAD2-4F01-A873-1302D1976436}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD3B410-924D-4470-A315-389056B4B4DD}">
   <dimension ref="B9:E114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23775,7 +23775,7 @@
         <v>43</v>
       </c>
       <c r="D17">
-        <v>0.53706666666666669</v>
+        <v>0.53706666666666658</v>
       </c>
       <c r="E17" t="s">
         <v>245</v>
@@ -23831,7 +23831,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.53259999999999996</v>
+        <v>0.53260000000000007</v>
       </c>
       <c r="E21" t="s">
         <v>245</v>
@@ -23901,7 +23901,7 @@
         <v>45</v>
       </c>
       <c r="D26">
-        <v>0.45539999999999997</v>
+        <v>0.45540000000000003</v>
       </c>
       <c r="E26" t="s">
         <v>245</v>
@@ -23915,7 +23915,7 @@
         <v>37</v>
       </c>
       <c r="D27">
-        <v>0.39490000000000003</v>
+        <v>0.39489999999999997</v>
       </c>
       <c r="E27" t="s">
         <v>245</v>
@@ -23971,7 +23971,7 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>0.4196333333333333</v>
+        <v>0.41963333333333336</v>
       </c>
       <c r="E31" t="s">
         <v>245</v>
@@ -24167,7 +24167,7 @@
         <v>43</v>
       </c>
       <c r="D45">
-        <v>0.34200000000000003</v>
+        <v>0.34199999999999992</v>
       </c>
       <c r="E45" t="s">
         <v>245</v>
@@ -24293,7 +24293,7 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <v>0.46533333333333332</v>
+        <v>0.46533333333333338</v>
       </c>
       <c r="E54" t="s">
         <v>245</v>
@@ -24391,7 +24391,7 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.43393333333333334</v>
+        <v>0.43393333333333328</v>
       </c>
       <c r="E61" t="s">
         <v>245</v>
@@ -24419,7 +24419,7 @@
         <v>37</v>
       </c>
       <c r="D63">
-        <v>0.37793333333333329</v>
+        <v>0.3779333333333334</v>
       </c>
       <c r="E63" t="s">
         <v>245</v>
@@ -24475,7 +24475,7 @@
         <v>37</v>
       </c>
       <c r="D67">
-        <v>0.49970000000000003</v>
+        <v>0.49969999999999998</v>
       </c>
       <c r="E67" t="s">
         <v>245</v>
@@ -24489,7 +24489,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.43366666666666664</v>
+        <v>0.4336666666666667</v>
       </c>
       <c r="E68" t="s">
         <v>245</v>
@@ -24531,7 +24531,7 @@
         <v>37</v>
       </c>
       <c r="D71">
-        <v>0.46956666666666669</v>
+        <v>0.46956666666666663</v>
       </c>
       <c r="E71" t="s">
         <v>245</v>
@@ -24587,7 +24587,7 @@
         <v>37</v>
       </c>
       <c r="D75">
-        <v>0.40233333333333338</v>
+        <v>0.40233333333333327</v>
       </c>
       <c r="E75" t="s">
         <v>245</v>
@@ -24615,7 +24615,7 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>0.46393333333333331</v>
+        <v>0.46393333333333336</v>
       </c>
       <c r="E77" t="s">
         <v>245</v>
@@ -24657,7 +24657,7 @@
         <v>41</v>
       </c>
       <c r="D80">
-        <v>0.37063333333333331</v>
+        <v>0.37063333333333337</v>
       </c>
       <c r="E80" t="s">
         <v>245</v>
@@ -24671,7 +24671,7 @@
         <v>43</v>
       </c>
       <c r="D81">
-        <v>0.48446666666666677</v>
+        <v>0.48446666666666666</v>
       </c>
       <c r="E81" t="s">
         <v>245</v>
@@ -24685,7 +24685,7 @@
         <v>45</v>
       </c>
       <c r="D82">
-        <v>0.39950000000000002</v>
+        <v>0.39949999999999997</v>
       </c>
       <c r="E82" t="s">
         <v>245</v>
@@ -24727,7 +24727,7 @@
         <v>43</v>
       </c>
       <c r="D85">
-        <v>0.41593333333333332</v>
+        <v>0.41593333333333327</v>
       </c>
       <c r="E85" t="s">
         <v>245</v>
@@ -24741,7 +24741,7 @@
         <v>45</v>
       </c>
       <c r="D86">
-        <v>0.40100000000000002</v>
+        <v>0.40099999999999997</v>
       </c>
       <c r="E86" t="s">
         <v>245</v>
@@ -24755,7 +24755,7 @@
         <v>37</v>
       </c>
       <c r="D87">
-        <v>0.42829999999999996</v>
+        <v>0.42830000000000007</v>
       </c>
       <c r="E87" t="s">
         <v>245</v>
@@ -24825,7 +24825,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.36646666666666672</v>
+        <v>0.36646666666666666</v>
       </c>
       <c r="E92" t="s">
         <v>245</v>
@@ -24909,7 +24909,7 @@
         <v>45</v>
       </c>
       <c r="D98">
-        <v>0.34030000000000005</v>
+        <v>0.34029999999999999</v>
       </c>
       <c r="E98" t="s">
         <v>245</v>
@@ -24937,7 +24937,7 @@
         <v>41</v>
       </c>
       <c r="D100">
-        <v>0.53963333333333341</v>
+        <v>0.5396333333333333</v>
       </c>
       <c r="E100" t="s">
         <v>245</v>
@@ -24993,7 +24993,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.50583333333333325</v>
+        <v>0.50583333333333336</v>
       </c>
       <c r="E104" t="s">
         <v>245</v>
@@ -25063,7 +25063,7 @@
         <v>43</v>
       </c>
       <c r="D109">
-        <v>0.39123333333333332</v>
+        <v>0.39123333333333338</v>
       </c>
       <c r="E109" t="s">
         <v>245</v>
@@ -25091,7 +25091,7 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.45906666666666668</v>
+        <v>0.45906666666666657</v>
       </c>
       <c r="E111" t="s">
         <v>245</v>
@@ -25119,7 +25119,7 @@
         <v>43</v>
       </c>
       <c r="D113">
-        <v>0.52856666666666663</v>
+        <v>0.52856666666666674</v>
       </c>
       <c r="E113" t="s">
         <v>245</v>
@@ -25133,7 +25133,7 @@
         <v>45</v>
       </c>
       <c r="D114">
-        <v>0.42776666666666663</v>
+        <v>0.42776666666666668</v>
       </c>
       <c r="E114" t="s">
         <v>245</v>
